--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1157,1517 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127647031</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>755449</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7211495</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127647063</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>755500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7211571</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127647058</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>755599</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7211666</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127647049</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>755535</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7211574</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127647062</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>755505</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7211588</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127647056</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>755613</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7211683</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127647050</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>755481</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7211502</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127647064</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>755467</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7211561</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127647061</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>755541</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7211580</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127647059</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>755621</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7211652</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127647023</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>755579</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7211594</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hona födosökande</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127647026</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>755602</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7211693</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127647046</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>755604</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7211684</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127647060</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>755594</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7211607</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127647057</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>755611</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7211684</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -2476,7 +2476,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R19" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R20" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -2476,7 +2476,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R19" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R20" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,32 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647031</v>
+        <v>127647063</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755449</v>
+        <v>755500</v>
       </c>
       <c r="R6" t="n">
-        <v>7211495</v>
+        <v>7211571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647063</v>
+        <v>127647058</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755500</v>
+        <v>755599</v>
       </c>
       <c r="R7" t="n">
-        <v>7211571</v>
+        <v>7211666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647058</v>
+        <v>127647031</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755599</v>
+        <v>755449</v>
       </c>
       <c r="R8" t="n">
-        <v>7211666</v>
+        <v>7211495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R19" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R20" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,32 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647063</v>
+        <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755500</v>
+        <v>755449</v>
       </c>
       <c r="R6" t="n">
-        <v>7211571</v>
+        <v>7211495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647058</v>
+        <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755599</v>
+        <v>755500</v>
       </c>
       <c r="R7" t="n">
-        <v>7211666</v>
+        <v>7211571</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647031</v>
+        <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755449</v>
+        <v>755599</v>
       </c>
       <c r="R8" t="n">
-        <v>7211495</v>
+        <v>7211666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127647057</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>127647060</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,32 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647031</v>
+        <v>127647058</v>
       </c>
       <c r="B6" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755449</v>
+        <v>755599</v>
       </c>
       <c r="R6" t="n">
-        <v>7211495</v>
+        <v>7211666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647058</v>
+        <v>127647031</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>98471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755599</v>
+        <v>755449</v>
       </c>
       <c r="R8" t="n">
-        <v>7211666</v>
+        <v>7211495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647058</v>
+        <v>127647063</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755599</v>
+        <v>755500</v>
       </c>
       <c r="R6" t="n">
-        <v>7211666</v>
+        <v>7211571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647063</v>
+        <v>127647058</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755500</v>
+        <v>755599</v>
       </c>
       <c r="R7" t="n">
-        <v>7211571</v>
+        <v>7211666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1356,7 +1356,7 @@
         <v>127647031</v>
       </c>
       <c r="B8" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647063</v>
+        <v>127647058</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755500</v>
+        <v>755599</v>
       </c>
       <c r="R6" t="n">
-        <v>7211571</v>
+        <v>7211666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647058</v>
+        <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755599</v>
+        <v>755500</v>
       </c>
       <c r="R7" t="n">
-        <v>7211666</v>
+        <v>7211571</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1356,7 @@
         <v>127647031</v>
       </c>
       <c r="B8" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647050</v>
+        <v>127647064</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755481</v>
+        <v>755467</v>
       </c>
       <c r="R12" t="n">
-        <v>7211502</v>
+        <v>7211561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647064</v>
+        <v>127647050</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755467</v>
+        <v>755481</v>
       </c>
       <c r="R13" t="n">
-        <v>7211561</v>
+        <v>7211502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R19" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R20" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647058</v>
+        <v>127647063</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755599</v>
+        <v>755500</v>
       </c>
       <c r="R6" t="n">
-        <v>7211666</v>
+        <v>7211571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647063</v>
+        <v>127647058</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755500</v>
+        <v>755599</v>
       </c>
       <c r="R7" t="n">
-        <v>7211571</v>
+        <v>7211666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1356,7 @@
         <v>127647031</v>
       </c>
       <c r="B8" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647064</v>
+        <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755467</v>
+        <v>755481</v>
       </c>
       <c r="R12" t="n">
-        <v>7211561</v>
+        <v>7211502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647050</v>
+        <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755481</v>
+        <v>755467</v>
       </c>
       <c r="R13" t="n">
-        <v>7211502</v>
+        <v>7211561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R19" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R20" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,32 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647063</v>
+        <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755500</v>
+        <v>755449</v>
       </c>
       <c r="R6" t="n">
-        <v>7211571</v>
+        <v>7211495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647058</v>
+        <v>127647063</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755599</v>
+        <v>755500</v>
       </c>
       <c r="R7" t="n">
-        <v>7211666</v>
+        <v>7211571</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647031</v>
+        <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>98488</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755449</v>
+        <v>755599</v>
       </c>
       <c r="R8" t="n">
-        <v>7211495</v>
+        <v>7211666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,32 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647031</v>
+        <v>127647063</v>
       </c>
       <c r="B6" t="n">
-        <v>98489</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755449</v>
+        <v>755500</v>
       </c>
       <c r="R6" t="n">
-        <v>7211495</v>
+        <v>7211571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647063</v>
+        <v>127647058</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755500</v>
+        <v>755599</v>
       </c>
       <c r="R7" t="n">
-        <v>7211571</v>
+        <v>7211666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647058</v>
+        <v>127647031</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>98490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755599</v>
+        <v>755449</v>
       </c>
       <c r="R8" t="n">
-        <v>7211666</v>
+        <v>7211495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1356,7 +1356,7 @@
         <v>127647031</v>
       </c>
       <c r="B8" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1159,32 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647063</v>
+        <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755500</v>
+        <v>755449</v>
       </c>
       <c r="R6" t="n">
-        <v>7211571</v>
+        <v>7211495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647058</v>
+        <v>127647063</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755599</v>
+        <v>755500</v>
       </c>
       <c r="R7" t="n">
-        <v>7211666</v>
+        <v>7211571</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647031</v>
+        <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755449</v>
+        <v>755599</v>
       </c>
       <c r="R8" t="n">
-        <v>7211495</v>
+        <v>7211666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R19" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R20" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -2476,7 +2476,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R19" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R20" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -2476,7 +2476,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647057</v>
+        <v>127647060</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755611</v>
+        <v>755594</v>
       </c>
       <c r="R19" t="n">
-        <v>7211684</v>
+        <v>7211607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647060</v>
+        <v>127647057</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755594</v>
+        <v>755611</v>
       </c>
       <c r="R20" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>98653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,14 +1252,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,14 +1353,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,14 +1454,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,14 +1560,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,14 +1661,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,14 +1762,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,14 +1863,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,14 +1964,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,14 +2070,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,14 +2171,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,14 +2289,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,14 +2398,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,14 +2520,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,14 +2621,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,7 +2722,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>127647023</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>127647026</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>127647046</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127647063</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>127647058</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>127647049</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127647062</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127647056</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>127647050</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127647064</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127647059</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127647060</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127647057</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>127647031</v>
       </c>
       <c r="B6" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106228458</v>
+        <v>106228421</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755623.7291918006</v>
+        <v>755624</v>
       </c>
       <c r="R2" t="n">
-        <v>7211689.418823629</v>
+        <v>7211689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +750,9 @@
           <t>2019-08-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,12 +783,7 @@
         <v>106228508</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755540.5775598607</v>
+        <v>755540</v>
       </c>
       <c r="R3" t="n">
-        <v>7211639.24845781</v>
+        <v>7211639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2019-08-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,19 +885,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106228481</v>
+        <v>106228458</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -954,11 +919,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755605.3371120859</v>
+        <v>755624</v>
       </c>
       <c r="R4" t="n">
-        <v>7211660.144151836</v>
+        <v>7211689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,19 +960,9 @@
           <t>2019-08-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,37 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106228421</v>
+        <v>106228481</v>
       </c>
       <c r="B5" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,7 +1024,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755623.7291918006</v>
+        <v>755605</v>
       </c>
       <c r="R5" t="n">
-        <v>7211689.418823629</v>
+        <v>7211660</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,19 +1069,9 @@
           <t>2019-08-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647031</v>
+        <v>127647049</v>
       </c>
       <c r="B6" t="n">
-        <v>98737</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755449</v>
+        <v>755535</v>
       </c>
       <c r="R6" t="n">
-        <v>7211495</v>
+        <v>7211574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,6 +1170,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,14 +1205,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647063</v>
+        <v>127647050</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1295,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755500</v>
+        <v>755481</v>
       </c>
       <c r="R7" t="n">
-        <v>7211571</v>
+        <v>7211502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,14 +1306,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647058</v>
+        <v>127647052</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1396,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755599</v>
+        <v>755489</v>
       </c>
       <c r="R8" t="n">
-        <v>7211666</v>
+        <v>7211713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,14 +1407,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647049</v>
+        <v>127647056</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1497,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755535</v>
+        <v>755613</v>
       </c>
       <c r="R9" t="n">
-        <v>7211574</v>
+        <v>7211683</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,11 +1478,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,14 +1508,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127647062</v>
+        <v>127647057</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1603,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755505</v>
+        <v>755611</v>
       </c>
       <c r="R10" t="n">
-        <v>7211588</v>
+        <v>7211684</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,14 +1609,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127647056</v>
+        <v>127647058</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1704,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755613</v>
+        <v>755599</v>
       </c>
       <c r="R11" t="n">
-        <v>7211683</v>
+        <v>7211666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,14 +1710,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647050</v>
+        <v>127647059</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1805,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755481</v>
+        <v>755621</v>
       </c>
       <c r="R12" t="n">
-        <v>7211502</v>
+        <v>7211652</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,14 +1811,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647064</v>
+        <v>127647060</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1906,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755467</v>
+        <v>755594</v>
       </c>
       <c r="R13" t="n">
-        <v>7211561</v>
+        <v>7211607</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,11 +1915,11 @@
         <v>127647061</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2078,14 +2018,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127647059</v>
+        <v>127647062</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2113,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755621</v>
+        <v>755505</v>
       </c>
       <c r="R15" t="n">
-        <v>7211652</v>
+        <v>7211588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,57 +2119,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127647023</v>
+        <v>127647063</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mullkälen, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755579</v>
+        <v>755500</v>
       </c>
       <c r="R16" t="n">
-        <v>7211594</v>
+        <v>7211571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,11 +2190,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hona födosökande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,53 +2220,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647026</v>
+        <v>127647064</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mullkälen, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755602</v>
+        <v>755467</v>
       </c>
       <c r="R17" t="n">
-        <v>7211693</v>
+        <v>7211561</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647046</v>
+        <v>127647023</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,11 +2349,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
@@ -2457,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755604</v>
+        <v>755579</v>
       </c>
       <c r="R18" t="n">
-        <v>7211684</v>
+        <v>7211594</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2408,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Hona födosökande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127647060</v>
+        <v>127647046</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,34 +2450,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mullkälen, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755594</v>
+        <v>755604</v>
       </c>
       <c r="R19" t="n">
-        <v>7211607</v>
+        <v>7211684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,6 +2526,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127647057</v>
+        <v>127647026</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2572,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mullkälen, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755611</v>
+        <v>755602</v>
       </c>
       <c r="R20" t="n">
-        <v>7211684</v>
+        <v>7211693</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,6 +2663,107 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127647031</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>755449</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7211495</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 62346-2023 artfynd.xlsx
+++ b/artfynd/A 62346-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106228421</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106228508</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106228458</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106228481</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647049</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647052</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647056</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647057</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647058</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647059</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647060</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647061</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647062</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647063</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647064</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2436,6 +2521,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647023</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647046</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2667,6 +2762,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2768,8 +2868,35 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647031</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>